--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_aysen.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_aysen.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:58</t>
+    <t xml:space="preserve">2026-09-09 19:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_aysen.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_aysen.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:23</t>
+    <t xml:space="preserve">2026-09-17 03:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_aysen.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_aysen.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 03:54</t>
+    <t xml:space="preserve">2026-09-27 02:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_aysen.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_aysen.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:18</t>
+    <t xml:space="preserve">2026-10-02 23:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_aysen.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_aysen.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">Territorio</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Mujeres</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 23:40</t>
+    <t xml:space="preserve">2026-10-05 05:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Aysen</t>
+    <t xml:space="preserve">Region de Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">Capitán Prat</t>
@@ -724,7 +721,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>95.28</v>
@@ -732,7 +729,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>86.29</v>
@@ -740,7 +737,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>167.61</v>
